--- a/dados/MelhorCenario.xlsx
+++ b/dados/MelhorCenario.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q27"/>
+  <dimension ref="A1:Q31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -537,7 +537,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PETRE301</t>
+          <t>PETRE284</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -547,7 +547,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>R$ 29.26</t>
+          <t>R$ 27.76</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -572,41 +572,41 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.6078</t>
+          <t>0.8520</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.9859</t>
+          <t>1.0000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>ATM → ITM</t>
+          <t>ITM → ITM</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Delta</t>
+          <t>Lote</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.15</v>
+        <v>100</v>
       </c>
       <c r="M2" t="n">
         <v>252</v>
       </c>
       <c r="N2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>R$ 549.28</t>
+          <t>R$ 399.07</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>R$ 791.01</t>
+          <t>R$ 624.74</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -618,7 +618,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PETRE306</t>
+          <t>PETRE289</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -628,7 +628,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>R$ 30.01</t>
+          <t>R$ 28.26</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -653,17 +653,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.4832</t>
+          <t>0.7833</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.6469</t>
+          <t>1.0000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>ATM → ATM</t>
+          <t>ITM → ITM</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -672,22 +672,22 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="M3" t="n">
-        <v>30</v>
+        <v>252</v>
       </c>
       <c r="N3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>R$ 525.56</t>
+          <t>R$ 535.16</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>R$ 850.75</t>
+          <t>R$ 909.85</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -699,7 +699,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PETRE312</t>
+          <t>PETRE301</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>R$ 30.51</t>
+          <t>R$ 29.26</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -734,41 +734,41 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.4168</t>
+          <t>0.6078</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.3714</t>
+          <t>0.9859</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>ATM → ATM</t>
+          <t>ATM → ITM</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Lote</t>
+          <t>Delta</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>300</v>
+        <v>0.15</v>
       </c>
       <c r="M4" t="n">
-        <v>30</v>
+        <v>252</v>
       </c>
       <c r="N4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>R$ 578.41</t>
+          <t>R$ 549.28</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>R$ 793.28</t>
+          <t>R$ 791.01</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -780,7 +780,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PETRE316</t>
+          <t>PETRE306</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -790,7 +790,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>R$ 31.01</t>
+          <t>R$ 30.01</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -815,53 +815,53 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.3536</t>
+          <t>0.4832</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.1535</t>
+          <t>0.6469</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>ATM → OTM</t>
+          <t>ATM → ATM</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Delta</t>
+          <t>Lote</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.1</v>
+        <v>300</v>
       </c>
       <c r="M5" t="n">
         <v>30</v>
       </c>
       <c r="N5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>R$ 834.81</t>
+          <t>R$ 525.56</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>R$ 835.13</t>
+          <t>R$ 850.75</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-05-07</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PETRE321</t>
+          <t>PETRE312</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>R$ 31.51</t>
+          <t>R$ 30.51</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -896,98 +896,98 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.2952</t>
+          <t>0.4168</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.0442</t>
+          <t>0.3714</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>OTM → OTM</t>
+          <t>ATM → ATM</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Delta</t>
+          <t>Lote</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.1</v>
+        <v>300</v>
       </c>
       <c r="M6" t="n">
         <v>30</v>
       </c>
       <c r="N6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>R$ 986.22</t>
+          <t>R$ 578.41</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>R$ 986.22</t>
+          <t>R$ 793.28</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-05-07</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PETRF303</t>
+          <t>PETRE316</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>R$ 28.94</t>
+          <t>R$ 31.01</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>R$ 30.22</t>
+          <t>R$ 29.39</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>R$ 32.23</t>
+          <t>R$ 30.09</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.7964</t>
+          <t>0.3536</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.0000</t>
+          <t>0.1535</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>ITM → ITM</t>
+          <t>ATM → OTM</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -999,112 +999,112 @@
         <v>0.1</v>
       </c>
       <c r="M7" t="n">
-        <v>252</v>
+        <v>30</v>
       </c>
       <c r="N7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>R$ 405.67</t>
+          <t>R$ 834.81</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>R$ 532.66</t>
+          <t>R$ 835.13</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2025-05-08</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PETRF321</t>
+          <t>PETRE321</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>R$ 30.69</t>
+          <t>R$ 31.51</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>R$ 30.22</t>
+          <t>R$ 29.39</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>R$ 32.23</t>
+          <t>R$ 30.09</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.5107</t>
+          <t>0.2952</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.9935</t>
+          <t>0.0442</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>ATM → ITM</t>
+          <t>OTM → OTM</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Dias</t>
+          <t>Delta</t>
         </is>
       </c>
       <c r="L8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>30</v>
+      </c>
+      <c r="N8" t="n">
         <v>3</v>
       </c>
-      <c r="M8" t="n">
-        <v>60</v>
-      </c>
-      <c r="N8" t="n">
-        <v>9</v>
-      </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>R$ -311.49</t>
+          <t>R$ 986.22</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>R$ 629.35</t>
+          <t>R$ 986.22</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2025-05-15</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PETRF326</t>
+          <t>PETRF303</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>R$ 31.19</t>
+          <t>R$ 28.94</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1139,17 +1139,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.4405</t>
+          <t>0.7964</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.9505</t>
+          <t>1.0000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>ATM → ITM</t>
+          <t>ITM → ITM</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1158,34 +1158,34 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="M9" t="n">
-        <v>60</v>
+        <v>252</v>
       </c>
       <c r="N9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>R$ 20.74</t>
+          <t>R$ 405.67</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>R$ 531.67</t>
+          <t>R$ 532.66</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-06-06</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PETRF331</t>
+          <t>PETRF321</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>R$ 29.69</t>
+          <t>R$ 30.69</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.6334</t>
+          <t>0.5107</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.0000</t>
+          <t>0.9935</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1235,38 +1235,38 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Delta</t>
+          <t>Dias</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0.15</v>
+        <v>3</v>
       </c>
       <c r="M10" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="N10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>R$ 699.60</t>
+          <t>R$ -311.49</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>R$ 699.60</t>
+          <t>R$ 629.35</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-06</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PETRF342</t>
+          <t>PETRF326</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>R$ 32.69</t>
+          <t>R$ 31.19</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1301,53 +1301,53 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.2959</t>
+          <t>0.4405</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.1488</t>
+          <t>0.9505</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>OTM → OTM</t>
+          <t>ATM → ITM</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Lote</t>
+          <t>Delta</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>300</v>
+        <v>0.15</v>
       </c>
       <c r="M11" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="N11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>R$ 509.95</t>
+          <t>R$ 20.74</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>R$ 509.95</t>
+          <t>R$ 531.67</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-11</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PETRF376</t>
+          <t>PETRF331</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>R$ 33.44</t>
+          <t>R$ 29.69</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1382,17 +1382,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.2288</t>
+          <t>0.6334</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.0045</t>
+          <t>1.0000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>OTM → OTM</t>
+          <t>ATM → ITM</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1407,16 +1407,16 @@
         <v>30</v>
       </c>
       <c r="N12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>R$ 498.37</t>
+          <t>R$ 699.60</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>R$ 498.37</t>
+          <t>R$ 699.60</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -1428,52 +1428,52 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PETRG307</t>
+          <t>PETRF342</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>R$ 29.23</t>
+          <t>R$ 32.69</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>R$ 31.66</t>
+          <t>R$ 30.22</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>R$ 31.07</t>
+          <t>R$ 32.23</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0.8568</t>
+          <t>0.2959</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.9999</t>
+          <t>0.1488</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>ITM → ITM</t>
+          <t>OTM → OTM</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1482,115 +1482,115 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="M13" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="N13" t="n">
         <v>2</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>R$ 807.41</t>
+          <t>R$ 509.95</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>R$ 807.41</t>
+          <t>R$ 509.95</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PETRG332</t>
+          <t>PETRF376</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>R$ 31.73</t>
+          <t>R$ 33.44</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>R$ 31.66</t>
+          <t>R$ 30.22</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>R$ 31.07</t>
+          <t>R$ 32.23</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.5656</t>
+          <t>0.2288</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.0165</t>
+          <t>0.0045</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>ATM → OTM</t>
+          <t>OTM → OTM</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Lote</t>
+          <t>Delta</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>300</v>
+        <v>0.15</v>
       </c>
       <c r="M14" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="N14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>R$ 1364.07</t>
+          <t>R$ 498.37</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>R$ 1364.07</t>
+          <t>R$ 498.37</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PETRG353</t>
+          <t>PETRG307</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>R$ 30.98</t>
+          <t>R$ 29.23</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1625,17 +1625,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.6656</t>
+          <t>0.8568</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.3324</t>
+          <t>0.9999</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>ATM → ATM</t>
+          <t>ITM → ITM</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1644,7 +1644,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="M15" t="n">
         <v>60</v>
@@ -1654,12 +1654,12 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>R$ 1267.63</t>
+          <t>R$ 807.41</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>R$ 1267.63</t>
+          <t>R$ 807.41</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -1671,7 +1671,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PETRG388</t>
+          <t>PETRG332</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1681,7 +1681,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>R$ 34.48</t>
+          <t>R$ 31.73</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1706,17 +1706,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.2273</t>
+          <t>0.5656</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0165</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>OTM → OTM</t>
+          <t>ATM → OTM</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1725,7 +1725,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="M16" t="n">
         <v>60</v>
@@ -1735,24 +1735,24 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>R$ 352.92</t>
+          <t>R$ 1364.07</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>R$ 357.59</t>
+          <t>R$ 1364.07</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2025-07-17</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PETRG398</t>
+          <t>PETRG353</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>R$ 35.48</t>
+          <t>R$ 30.98</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1787,88 +1787,88 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.0740</t>
+          <t>0.6656</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.3324</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>OTM → OTM</t>
+          <t>ATM → ATM</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Delta</t>
+          <t>Lote</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0.15</v>
+        <v>300</v>
       </c>
       <c r="M17" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="N17" t="n">
         <v>2</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>R$ 234.10</t>
+          <t>R$ 1267.63</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>R$ 308.51</t>
+          <t>R$ 1267.63</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-17</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>PETRH1</t>
+          <t>PETRG388</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>R$ 35.23</t>
+          <t>R$ 34.48</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>R$ 31.52</t>
+          <t>R$ 31.66</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>R$ 30.05</t>
+          <t>R$ 31.07</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.1008</t>
+          <t>0.2273</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1887,69 +1887,69 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="M18" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="N18" t="n">
         <v>3</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>R$ 157.85</t>
+          <t>R$ 352.92</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>R$ 157.89</t>
+          <t>R$ 357.59</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-07-16</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PETRH335</t>
+          <t>PETRG398</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>R$ 31.98</t>
+          <t>R$ 35.48</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>R$ 31.52</t>
+          <t>R$ 31.66</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>R$ 30.05</t>
+          <t>R$ 31.07</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.5097</t>
+          <t>0.0740</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>ATM → OTM</t>
+          <t>OTM → OTM</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1971,31 +1971,31 @@
         <v>0.15</v>
       </c>
       <c r="M19" t="n">
-        <v>252</v>
+        <v>30</v>
       </c>
       <c r="N19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>R$ 762.73</t>
+          <t>R$ 234.10</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>R$ 828.27</t>
+          <t>R$ 308.51</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-07-11</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PETRH345</t>
+          <t>PETRH1</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>R$ 32.98</t>
+          <t>R$ 35.23</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.3489</t>
+          <t>0.1008</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2040,7 +2040,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>ATM → OTM</t>
+          <t>OTM → OTM</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="M20" t="n">
         <v>30</v>
@@ -2059,12 +2059,12 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>R$ 623.22</t>
+          <t>R$ 157.85</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>R$ 648.72</t>
+          <t>R$ 157.89</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -2076,7 +2076,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PETRH369</t>
+          <t>PETRH304</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>R$ 36.23</t>
+          <t>R$ 29.73</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2111,341 +2111,341 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.0340</t>
+          <t>0.8310</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.3478</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>OTM → OTM</t>
+          <t>ITM → ATM</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Dias</t>
+          <t>Delta</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>7</v>
+        <v>0.15</v>
       </c>
       <c r="M21" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="N21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>R$ 71.73</t>
+          <t>R$ 394.95</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>R$ 71.73</t>
+          <t>R$ 394.95</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-14</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PETRI28</t>
+          <t>PETRH310</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>R$ 28.22</t>
+          <t>R$ 30.23</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>R$ 29.53</t>
+          <t>R$ 31.52</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>R$ 31.77</t>
+          <t>R$ 30.05</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.8163</t>
+          <t>0.7721</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.0000</t>
+          <t>0.0858</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>ITM → ITM</t>
+          <t>ITM → OTM</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Dias</t>
+          <t>Delta</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="M22" t="n">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="N22" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>R$ 624.50</t>
+          <t>R$ 1131.52</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>R$ 664.50</t>
+          <t>R$ 1131.52</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-08-14</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>PETRI288</t>
+          <t>PETRH335</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>R$ 27.47</t>
+          <t>R$ 31.98</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>R$ 29.53</t>
+          <t>R$ 31.52</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>R$ 31.77</t>
+          <t>R$ 30.05</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.9027</t>
+          <t>0.5097</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.0000</t>
+          <t>0.0000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>ITM → ITM</t>
+          <t>ATM → OTM</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Dias</t>
+          <t>Delta</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1</v>
+        <v>0.15</v>
       </c>
       <c r="M23" t="n">
-        <v>30</v>
+        <v>252</v>
       </c>
       <c r="N23" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>R$ 462.30</t>
+          <t>R$ 762.73</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>R$ 462.30</t>
+          <t>R$ 828.27</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-08-12</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>PETRI29</t>
+          <t>PETRH345</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>R$ 28.97</t>
+          <t>R$ 32.98</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>R$ 29.53</t>
+          <t>R$ 31.52</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>R$ 31.77</t>
+          <t>R$ 30.05</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.6910</t>
+          <t>0.3489</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.0000</t>
+          <t>0.0000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>ATM → ITM</t>
+          <t>ATM → OTM</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Dias</t>
+          <t>Lote</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>300</v>
       </c>
       <c r="M24" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="N24" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>R$ 466.71</t>
+          <t>R$ 623.22</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>R$ 506.71</t>
+          <t>R$ 648.72</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-08-11</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PETRI313</t>
+          <t>PETRH369</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>R$ 29.22</t>
+          <t>R$ 36.23</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>R$ 29.53</t>
+          <t>R$ 31.52</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>R$ 31.77</t>
+          <t>R$ 30.05</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.6471</t>
+          <t>0.0340</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.0000</t>
+          <t>0.0000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>ATM → ITM</t>
+          <t>OTM → OTM</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2454,34 +2454,34 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="M25" t="n">
         <v>60</v>
       </c>
       <c r="N25" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>R$ 510.65</t>
+          <t>R$ 71.73</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>R$ 570.65</t>
+          <t>R$ 71.73</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-08-12</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PETRI333</t>
+          <t>PETRI28</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>R$ 31.22</t>
+          <t>R$ 28.22</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2516,17 +2516,17 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>0.3191</t>
+          <t>0.8163</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.6611</t>
+          <t>1.0000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>ATM → ATM</t>
+          <t>ITM → ITM</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2538,103 +2538,427 @@
         <v>1</v>
       </c>
       <c r="M26" t="n">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="N26" t="n">
         <v>23</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>R$ 749.88</t>
+          <t>R$ 624.50</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>R$ 749.88</t>
+          <t>R$ 664.50</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>PETRI288</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>R$ 27.47</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>R$ 29.53</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>R$ 31.77</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>0.9027</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1.0000</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>ITM → ITM</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Dias</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>1</v>
+      </c>
+      <c r="M27" t="n">
+        <v>30</v>
+      </c>
+      <c r="N27" t="n">
+        <v>23</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>R$ 462.30</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>R$ 462.30</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>PETRI29</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>R$ 28.97</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>R$ 29.53</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>R$ 31.77</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>0.6910</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1.0000</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>ATM → ITM</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Dias</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>1</v>
+      </c>
+      <c r="M28" t="n">
+        <v>60</v>
+      </c>
+      <c r="N28" t="n">
+        <v>23</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>R$ 466.71</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>R$ 506.71</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>PETRI313</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>R$ 29.22</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>R$ 29.53</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>R$ 31.77</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>0.6471</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1.0000</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>ATM → ITM</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Dias</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>1</v>
+      </c>
+      <c r="M29" t="n">
+        <v>60</v>
+      </c>
+      <c r="N29" t="n">
+        <v>23</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>R$ 510.65</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>R$ 570.65</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>PETRI333</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>R$ 31.22</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>R$ 29.53</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>R$ 31.77</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>0.3191</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>0.6611</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>ATM → ATM</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Dias</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>1</v>
+      </c>
+      <c r="M30" t="n">
+        <v>120</v>
+      </c>
+      <c r="N30" t="n">
+        <v>23</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>R$ 749.88</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>R$ 749.88</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>PETRI341</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>2025-09-19</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>R$ 31.97</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>2025-09-18</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>R$ 29.53</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>R$ 31.77</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>0.2238</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>0.1502</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>OTM → OTM</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>Lote</t>
         </is>
       </c>
-      <c r="L27" t="n">
+      <c r="L31" t="n">
         <v>100</v>
       </c>
-      <c r="M27" t="n">
+      <c r="M31" t="n">
         <v>120</v>
       </c>
-      <c r="N27" t="n">
+      <c r="N31" t="n">
         <v>3</v>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>R$ 658.49</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>R$ 706.12</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="Q31" t="inlineStr">
         <is>
           <t>2025-09-17</t>
         </is>
